--- a/data/trans_dic/P16A08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A08-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,35</t>
+          <t>2,37; 6,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,6</t>
+          <t>2,64; 6,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,64</t>
+          <t>2,01; 5,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,09</t>
+          <t>1,7; 6,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,76</t>
+          <t>1,23; 5,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 8,67</t>
+          <t>3,45; 8,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,56</t>
+          <t>2,78; 7,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,98</t>
+          <t>3,82; 8,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,03</t>
+          <t>2,31; 4,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,7</t>
+          <t>3,47; 6,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,83</t>
+          <t>2,84; 5,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,18</t>
+          <t>3,13; 5,91</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,64</t>
+          <t>2,67; 7,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,04</t>
+          <t>2,01; 5,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,69</t>
+          <t>1,92; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,12</t>
+          <t>4,31; 10,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,95</t>
+          <t>4,63; 9,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,44</t>
+          <t>3,41; 8,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 10,27</t>
+          <t>5,36; 10,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,29</t>
+          <t>2,49; 5,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,69</t>
+          <t>3,89; 7,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,44</t>
+          <t>3,14; 6,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,96</t>
+          <t>3,96; 6,89</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,31</t>
+          <t>1,45; 4,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,33</t>
+          <t>1,96; 5,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,24</t>
+          <t>1,23; 4,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,17</t>
+          <t>0,79; 5,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,17</t>
+          <t>0,53; 5,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,22</t>
+          <t>2,8; 8,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,62</t>
+          <t>4,73; 13,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,8</t>
+          <t>3,14; 8,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,92</t>
+          <t>1,42; 3,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,37</t>
+          <t>2,64; 5,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,53</t>
+          <t>2,54; 5,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,34</t>
+          <t>1,43; 5,4</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,5</t>
+          <t>1,6; 3,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,41</t>
+          <t>1,55; 3,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,45</t>
+          <t>1,59; 3,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,34</t>
+          <t>1,95; 4,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,84</t>
+          <t>2,88; 5,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,32</t>
+          <t>5,46; 9,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,8</t>
+          <t>4,49; 8,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,14</t>
+          <t>1,7; 5,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,97</t>
+          <t>2,27; 3,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,43</t>
+          <t>3,39; 5,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 4,93</t>
+          <t>3,12; 4,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,21</t>
+          <t>2,18; 4,14</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,39</t>
+          <t>0,54; 3,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,84</t>
+          <t>1,64; 4,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,0</t>
+          <t>2,0; 4,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,24</t>
+          <t>2,3; 6,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,33</t>
+          <t>2,18; 5,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,76</t>
+          <t>2,74; 5,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,2</t>
+          <t>3,7; 7,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 36,01</t>
+          <t>3,45; 35,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,03</t>
+          <t>1,77; 3,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,73</t>
+          <t>2,67; 4,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,47</t>
+          <t>3,25; 5,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 26,45</t>
+          <t>3,6; 23,47</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,71</t>
+          <t>1,14; 4,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,24</t>
+          <t>3,65; 9,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,88</t>
+          <t>2,7; 8,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,65</t>
+          <t>1,15; 12,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,91</t>
+          <t>2,72; 4,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,49</t>
+          <t>3,71; 6,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,34</t>
+          <t>3,42; 6,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,26</t>
+          <t>2,63; 5,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,39</t>
+          <t>2,65; 4,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,39</t>
+          <t>4,15; 6,58</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 5,98</t>
+          <t>3,66; 5,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,91</t>
+          <t>2,65; 5,67</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,03</t>
+          <t>1,87; 2,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,12</t>
+          <t>2,72; 4,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,77</t>
+          <t>2,54; 3,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,06</t>
+          <t>2,34; 4,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,63</t>
+          <t>3,35; 4,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 6,45</t>
+          <t>4,86; 6,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,28</t>
+          <t>4,64; 6,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,89</t>
+          <t>4,17; 13,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,67</t>
+          <t>2,77; 3,63</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,05</t>
+          <t>3,96; 5,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 4,74</t>
+          <t>3,77; 4,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,57</t>
+          <t>3,61; 9,11</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12130; 30101</t>
+          <t>11216; 30944</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11394; 28843</t>
+          <t>11552; 28174</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8491; 24210</t>
+          <t>8621; 24741</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8480; 30770</t>
+          <t>8594; 30402</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3631; 14612</t>
+          <t>3764; 15516</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10591; 27165</t>
+          <t>10823; 27386</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9195; 26220</t>
+          <t>9655; 27467</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16663; 35702</t>
+          <t>17102; 36204</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18314; 39239</t>
+          <t>18039; 38785</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25561; 50306</t>
+          <t>26046; 49511</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22449; 45270</t>
+          <t>22070; 45430</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29801; 58847</t>
+          <t>29821; 56324</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7890</t>
+          <t>0; 6513</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11083; 31863</t>
+          <t>11142; 32427</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7452; 22777</t>
+          <t>7590; 22328</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8950; 25737</t>
+          <t>8679; 25433</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15941; 37637</t>
+          <t>16037; 37939</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14932; 33356</t>
+          <t>15534; 33458</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13147; 31428</t>
+          <t>12709; 30794</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20762; 39293</t>
+          <t>20521; 40012</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17154; 39050</t>
+          <t>18388; 39874</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30366; 57854</t>
+          <t>29301; 58055</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24037; 48239</t>
+          <t>23550; 46474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32448; 58099</t>
+          <t>33033; 57513</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8466; 23370</t>
+          <t>7884; 24353</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12347; 33404</t>
+          <t>12303; 34295</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6553; 22120</t>
+          <t>6439; 21873</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6018; 34562</t>
+          <t>5284; 36863</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>892; 8675</t>
+          <t>892; 8500</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6977; 21209</t>
+          <t>7212; 21599</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8041; 22630</t>
+          <t>7863; 22691</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5165; 14683</t>
+          <t>5246; 14270</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10799; 27837</t>
+          <t>10103; 26988</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22379; 47492</t>
+          <t>23319; 48940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17055; 38039</t>
+          <t>17459; 37717</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10051; 44621</t>
+          <t>11955; 45091</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18951; 43399</t>
+          <t>19825; 43228</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18387; 39454</t>
+          <t>17907; 39890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18909; 39654</t>
+          <t>18333; 40105</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20539; 44911</t>
+          <t>20191; 45253</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20571; 41711</t>
+          <t>20583; 41551</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42540; 71432</t>
+          <t>41849; 73041</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36831; 64422</t>
+          <t>37120; 66432</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16609; 50222</t>
+          <t>16634; 50501</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46277; 77442</t>
+          <t>44291; 76317</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65815; 104497</t>
+          <t>65144; 103606</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62662; 97344</t>
+          <t>61552; 97974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44440; 84742</t>
+          <t>43790; 83226</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1971; 11840</t>
+          <t>1872; 11746</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8680; 24720</t>
+          <t>8384; 25387</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12693; 31006</t>
+          <t>12408; 30133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11452; 29532</t>
+          <t>10904; 28725</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12345; 30318</t>
+          <t>12382; 30923</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20714; 43713</t>
+          <t>20775; 44161</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27583; 53175</t>
+          <t>27335; 53299</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29417; 302081</t>
+          <t>28917; 294043</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15878; 36990</t>
+          <t>16265; 36333</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32286; 59960</t>
+          <t>33847; 60518</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44004; 74378</t>
+          <t>44186; 75113</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45817; 347114</t>
+          <t>47258; 308002</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3529; 14053</t>
+          <t>3414; 14078</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8858; 24554</t>
+          <t>9715; 26495</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7907; 22635</t>
+          <t>7757; 23575</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2773; 25607</t>
+          <t>2764; 28877</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35148; 61357</t>
+          <t>33972; 61057</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42839; 71722</t>
+          <t>41036; 70221</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37644; 68608</t>
+          <t>36954; 66659</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19787; 39958</t>
+          <t>20009; 40276</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39741; 67890</t>
+          <t>41015; 69496</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53825; 87658</t>
+          <t>56961; 90219</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50629; 81883</t>
+          <t>50066; 81814</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>26258; 59099</t>
+          <t>26505; 56739</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>61055; 98951</t>
+          <t>61148; 97292</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>94174; 140681</t>
+          <t>92705; 140226</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85699; 127733</t>
+          <t>85870; 128308</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81864; 137087</t>
+          <t>78842; 139397</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>111178; 156515</t>
+          <t>113163; 157795</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>169579; 227983</t>
+          <t>171851; 225421</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>164577; 221626</t>
+          <t>163757; 219150</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>147493; 460706</t>
+          <t>148888; 485790</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>183708; 243869</t>
+          <t>183915; 240965</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>276782; 351286</t>
+          <t>275536; 347986</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>261846; 328132</t>
+          <t>261074; 329811</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>250076; 664764</t>
+          <t>250852; 633255</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A08-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,53</t>
+          <t>2,44; 6,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,44</t>
+          <t>2,47; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,77</t>
+          <t>2,16; 5,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,02</t>
+          <t>1,66; 5,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,06</t>
+          <t>1,25; 4,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,74</t>
+          <t>3,44; 8,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,91</t>
+          <t>2,93; 7,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,09</t>
+          <t>3,75; 7,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,97</t>
+          <t>2,24; 5,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,6</t>
+          <t>3,44; 6,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,85</t>
+          <t>2,7; 5,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,91</t>
+          <t>3,11; 5,69</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,78</t>
+          <t>2,6; 7,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,92</t>
+          <t>2,02; 6,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,62</t>
+          <t>2,13; 5,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,2</t>
+          <t>4,43; 9,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,98</t>
+          <t>4,44; 10,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,27</t>
+          <t>3,5; 8,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,46</t>
+          <t>5,31; 10,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,4</t>
+          <t>2,49; 5,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,72</t>
+          <t>4,04; 7,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,2</t>
+          <t>3,24; 6,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,89</t>
+          <t>3,96; 6,79</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,49</t>
+          <t>1,56; 4,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,48</t>
+          <t>1,92; 5,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,19</t>
+          <t>1,33; 4,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,52</t>
+          <t>2,56; 6,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,07</t>
+          <t>0,53; 4,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,37</t>
+          <t>2,85; 8,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 13,66</t>
+          <t>4,63; 13,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,55</t>
+          <t>3,3; 9,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,8</t>
+          <t>1,55; 3,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,53</t>
+          <t>2,65; 5,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,48</t>
+          <t>2,47; 5,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,4</t>
+          <t>3,19; 6,55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,49</t>
+          <t>1,6; 3,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,45</t>
+          <t>1,54; 3,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,49</t>
+          <t>1,57; 3,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,37</t>
+          <t>2,01; 4,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,82</t>
+          <t>2,82; 5,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,53</t>
+          <t>5,43; 9,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,04</t>
+          <t>4,49; 7,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,17</t>
+          <t>3,51; 5,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,91</t>
+          <t>2,27; 3,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,39</t>
+          <t>3,34; 5,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,96</t>
+          <t>3,17; 4,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,14</t>
+          <t>2,98; 4,7</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,36</t>
+          <t>0,6; 3,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,97</t>
+          <t>1,66; 4,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,85</t>
+          <t>2,18; 4,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,07</t>
+          <t>2,18; 5,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,44</t>
+          <t>2,02; 5,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,82</t>
+          <t>2,76; 5,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,22</t>
+          <t>3,73; 6,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 35,05</t>
+          <t>3,5; 6,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,96</t>
+          <t>1,86; 3,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,77</t>
+          <t>2,63; 4,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,53</t>
+          <t>3,41; 5,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 23,47</t>
+          <t>3,32; 5,23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,72</t>
+          <t>1,16; 4,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,97</t>
+          <t>3,36; 10,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,21</t>
+          <t>2,71; 8,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 12,01</t>
+          <t>0,95; 7,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,89</t>
+          <t>2,71; 4,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,35</t>
+          <t>3,73; 6,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,16</t>
+          <t>3,5; 6,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,3</t>
+          <t>2,55; 5,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,49</t>
+          <t>2,69; 4,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,58</t>
+          <t>4,11; 6,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,98</t>
+          <t>3,65; 5,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,67</t>
+          <t>2,6; 5,19</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 2,98</t>
+          <t>1,84; 2,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,11</t>
+          <t>2,76; 4,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,79</t>
+          <t>2,51; 3,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,13</t>
+          <t>2,76; 4,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,67</t>
+          <t>3,3; 4,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,37</t>
+          <t>4,81; 6,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,21</t>
+          <t>4,68; 6,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 13,59</t>
+          <t>4,3; 5,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,63</t>
+          <t>2,77; 3,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 5,01</t>
+          <t>3,98; 5,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 4,77</t>
+          <t>3,77; 4,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,11</t>
+          <t>3,72; 4,63</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41184</t>
+          <t>44179</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11216; 30944</t>
+          <t>11548; 29148</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11552; 28174</t>
+          <t>10806; 27732</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8621; 24741</t>
+          <t>9266; 24990</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8594; 30402</t>
+          <t>9151; 30410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3764; 15516</t>
+          <t>3846; 14584</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10823; 27386</t>
+          <t>10765; 26735</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9655; 27467</t>
+          <t>10158; 27543</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17102; 36204</t>
+          <t>18331; 37289</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18039; 38785</t>
+          <t>17486; 41165</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26046; 49511</t>
+          <t>25807; 48794</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22070; 45430</t>
+          <t>20989; 44676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29821; 56324</t>
+          <t>32352; 59132</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28473</t>
+          <t>31710</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43485</t>
+          <t>47775</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6513</t>
+          <t>0; 7052</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11142; 32427</t>
+          <t>10833; 30661</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7590; 22328</t>
+          <t>7618; 24505</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8679; 25433</t>
+          <t>10304; 26810</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16037; 37939</t>
+          <t>16489; 36134</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15534; 33458</t>
+          <t>14882; 35377</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12709; 30794</t>
+          <t>13023; 29819</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20521; 40012</t>
+          <t>22481; 42426</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18388; 39874</t>
+          <t>18402; 39968</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29301; 58055</t>
+          <t>30376; 59367</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23550; 46474</t>
+          <t>24259; 48144</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33033; 57513</t>
+          <t>35870; 61542</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18739</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27768</t>
+          <t>30868</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7884; 24353</t>
+          <t>8462; 24867</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12303; 34295</t>
+          <t>12055; 32903</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6439; 21873</t>
+          <t>6925; 23151</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5284; 36863</t>
+          <t>12085; 31453</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>892; 8500</t>
+          <t>897; 8333</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7212; 21599</t>
+          <t>7350; 21413</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7863; 22691</t>
+          <t>7687; 22910</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5246; 14270</t>
+          <t>6188; 17388</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10103; 26988</t>
+          <t>10991; 27697</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23319; 48940</t>
+          <t>23411; 47636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17459; 37717</t>
+          <t>16991; 37672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11955; 45091</t>
+          <t>21051; 43185</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>34900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35699</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65151</t>
+          <t>74784</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19825; 43228</t>
+          <t>19811; 42753</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17907; 39890</t>
+          <t>17835; 40961</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18333; 40105</t>
+          <t>18077; 39572</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20191; 45253</t>
+          <t>22791; 47673</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20583; 41551</t>
+          <t>20168; 40491</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41849; 73041</t>
+          <t>41664; 73563</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37120; 66432</t>
+          <t>37087; 65147</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16634; 50501</t>
+          <t>30231; 49985</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44291; 76317</t>
+          <t>44292; 76069</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65144; 103606</t>
+          <t>64335; 102168</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61552; 97974</t>
+          <t>62541; 96984</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43790; 83226</t>
+          <t>59322; 93684</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>98985</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>117767</t>
+          <t>58305</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1872; 11746</t>
+          <t>2105; 12326</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8384; 25387</t>
+          <t>8479; 24433</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12408; 30133</t>
+          <t>13555; 30839</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10904; 28725</t>
+          <t>12328; 30474</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12382; 30923</t>
+          <t>11463; 30800</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20775; 44161</t>
+          <t>20901; 42810</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27335; 53299</t>
+          <t>27508; 51256</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28917; 294043</t>
+          <t>29077; 49824</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16265; 36333</t>
+          <t>17082; 35973</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33847; 60518</t>
+          <t>33417; 62054</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44186; 75113</t>
+          <t>46308; 79228</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>47258; 308002</t>
+          <t>46334; 72974</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27711</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37558</t>
+          <t>39195</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3414; 14078</t>
+          <t>3449; 14162</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9715; 26495</t>
+          <t>8923; 27051</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7757; 23575</t>
+          <t>7796; 23288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2764; 28877</t>
+          <t>2265; 17847</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33972; 61057</t>
+          <t>33868; 60974</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41036; 70221</t>
+          <t>41223; 71752</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36954; 66659</t>
+          <t>37872; 67781</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20009; 40276</t>
+          <t>21522; 45719</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41015; 69496</t>
+          <t>41679; 69904</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56961; 90219</t>
+          <t>56329; 90311</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50066; 81814</t>
+          <t>50014; 81304</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>26505; 56739</t>
+          <t>28045; 56056</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108369</t>
+          <t>115428</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>224543</t>
+          <t>179679</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>332912</t>
+          <t>295107</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>61148; 97292</t>
+          <t>59995; 97033</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>92705; 140226</t>
+          <t>94352; 141282</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85870; 128308</t>
+          <t>84813; 127933</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78842; 139397</t>
+          <t>94850; 142524</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>113163; 157795</t>
+          <t>111518; 159036</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>171851; 225421</t>
+          <t>170087; 226193</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>163757; 219150</t>
+          <t>165109; 220938</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>148888; 485790</t>
+          <t>156347; 204416</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>183915; 240965</t>
+          <t>184000; 238905</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>275536; 347986</t>
+          <t>276535; 350802</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>261074; 329811</t>
+          <t>260618; 328514</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>250852; 633255</t>
+          <t>262879; 327736</t>
         </is>
       </c>
     </row>
